--- a/src/components/study/excel/topics/009_001_information-and-cell-inspection-functions/excel_files/information_and_cell_inspection_functions_master.xlsx
+++ b/src/components/study/excel/topics/009_001_information-and-cell-inspection-functions/excel_files/information_and_cell_inspection_functions_master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="345">
   <si>
     <t>CODER &amp; ACCOTAX - INFORMATION &amp; CELL INSPECTION FUNCTIONS WORKBOOK</t>
   </si>
@@ -129,10 +129,10 @@
     <t>Evaluated Result</t>
   </si>
   <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>Kolkata Branch</t>
+    <t>Cell_B4</t>
+  </si>
+  <si>
+    <t>Swadeep Hui</t>
   </si>
   <si>
     <t>=ISTEXT(B4)</t>
@@ -141,7 +141,10 @@
     <t>TRUE</t>
   </si>
   <si>
-    <t>A5</t>
+    <t>Cell_B5</t>
+  </si>
+  <si>
+    <t>Tuhina Das</t>
   </si>
   <si>
     <t>=ISTEXT(B5)</t>
@@ -150,175 +153,907 @@
     <t>FALSE</t>
   </si>
   <si>
+    <t>Cell_B6</t>
+  </si>
+  <si>
+    <t>Abhronila Ray</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B6)</t>
+  </si>
+  <si>
+    <t>Cell_B7</t>
+  </si>
+  <si>
+    <t>Susmita Sen</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B7)</t>
+  </si>
+  <si>
+    <t>Cell_B8</t>
+  </si>
+  <si>
+    <t>Debangshu Roy</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B8)</t>
+  </si>
+  <si>
+    <t>Cell_B9</t>
+  </si>
+  <si>
+    <t>Rahul Kumar</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B9)</t>
+  </si>
+  <si>
+    <t>Cell_B10</t>
+  </si>
+  <si>
+    <t>Priya Sharma</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B10)</t>
+  </si>
+  <si>
+    <t>Cell_B11</t>
+  </si>
+  <si>
+    <t>Aniket Verma</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B11)</t>
+  </si>
+  <si>
+    <t>Cell_B12</t>
+  </si>
+  <si>
+    <t>Sourav Ganguly</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B12)</t>
+  </si>
+  <si>
+    <t>Cell_B13</t>
+  </si>
+  <si>
+    <t>Sneha Ghosh</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B13)</t>
+  </si>
+  <si>
+    <t>Cell_B14</t>
+  </si>
+  <si>
+    <t>Arpan Dey</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B14)</t>
+  </si>
+  <si>
+    <t>Cell_B15</t>
+  </si>
+  <si>
+    <t>Subhajit Pal</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B15)</t>
+  </si>
+  <si>
+    <t>Cell_B16</t>
+  </si>
+  <si>
+    <t>Riya Sarkar</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B16)</t>
+  </si>
+  <si>
+    <t>Cell_B17</t>
+  </si>
+  <si>
+    <t>Dipankar Mitra</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B17)</t>
+  </si>
+  <si>
+    <t>Cell_B18</t>
+  </si>
+  <si>
+    <t>Barnali Dutta</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B18)</t>
+  </si>
+  <si>
+    <t>Cell_B19</t>
+  </si>
+  <si>
+    <t>Vikram Singh</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B19)</t>
+  </si>
+  <si>
+    <t>Cell_B20</t>
+  </si>
+  <si>
+    <t>Kavita Nair</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B20)</t>
+  </si>
+  <si>
+    <t>Cell_B21</t>
+  </si>
+  <si>
+    <t>Amitabh Basu</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B21)</t>
+  </si>
+  <si>
+    <t>Cell_B22</t>
+  </si>
+  <si>
+    <t>Pooja Bannerjee</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B22)</t>
+  </si>
+  <si>
+    <t>Cell_B23</t>
+  </si>
+  <si>
+    <t>Sanjay Chakraborty</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B23)</t>
+  </si>
+  <si>
+    <t>Cell_B24</t>
+  </si>
+  <si>
+    <t>Tanmoy Das</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B24)</t>
+  </si>
+  <si>
+    <t>Cell_B25</t>
+  </si>
+  <si>
+    <t>Mousumi Mukhopadhyay</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B25)</t>
+  </si>
+  <si>
+    <t>Cell_B26</t>
+  </si>
+  <si>
+    <t>Bikash Chatterjee</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B26)</t>
+  </si>
+  <si>
+    <t>Cell_B27</t>
+  </si>
+  <si>
+    <t>Sayani Bose</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B27)</t>
+  </si>
+  <si>
+    <t>Cell_B28</t>
+  </si>
+  <si>
+    <t>Aritra Sen</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B28)</t>
+  </si>
+  <si>
+    <t>Cell_B29</t>
+  </si>
+  <si>
+    <t>Niladri Roy</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B29)</t>
+  </si>
+  <si>
+    <t>Cell_B30</t>
+  </si>
+  <si>
+    <t>Paromita Guha</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B30)</t>
+  </si>
+  <si>
+    <t>Cell_B31</t>
+  </si>
+  <si>
+    <t>Siddharth Mallick</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B31)</t>
+  </si>
+  <si>
+    <t>Cell_B32</t>
+  </si>
+  <si>
+    <t>Trisha Roy</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B32)</t>
+  </si>
+  <si>
+    <t>Cell_B33</t>
+  </si>
+  <si>
+    <t>Kaushik Hazra</t>
+  </si>
+  <si>
+    <t>=ISTEXT(B33)</t>
+  </si>
+  <si>
     <t>INFORMATION AUDIT LAB: ISNONTEXT (Non-Text Verification)</t>
   </si>
   <si>
     <t>=ISNONTEXT(B4)</t>
   </si>
   <si>
-    <t>Verified</t>
-  </si>
-  <si>
     <t>=ISNONTEXT(B5)</t>
   </si>
   <si>
+    <t>=ISNONTEXT(B6)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B7)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B8)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B9)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B10)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B11)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B12)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B13)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B14)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B15)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B16)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B17)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B18)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B19)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B20)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B21)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B22)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B23)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B24)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B25)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B26)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B27)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B28)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B29)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B30)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B31)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B32)</t>
+  </si>
+  <si>
+    <t>=ISNONTEXT(B33)</t>
+  </si>
+  <si>
     <t>INFORMATION AUDIT LAB: ISREF (Cell Reference Validation)</t>
   </si>
   <si>
-    <t>Ref_String</t>
-  </si>
-  <si>
-    <t>B4:B10</t>
-  </si>
-  <si>
-    <t>=ISREF(INDIRECT(A4))</t>
-  </si>
-  <si>
-    <t>Invalid_Name</t>
-  </si>
-  <si>
-    <t>=ISREF(INDIRECT(A5))</t>
+    <t>=ISREF(B4)</t>
+  </si>
+  <si>
+    <t>=ISREF(B5)</t>
+  </si>
+  <si>
+    <t>=ISREF(B6)</t>
+  </si>
+  <si>
+    <t>=ISREF(B7)</t>
+  </si>
+  <si>
+    <t>=ISREF(B8)</t>
+  </si>
+  <si>
+    <t>=ISREF(B9)</t>
+  </si>
+  <si>
+    <t>=ISREF(B10)</t>
+  </si>
+  <si>
+    <t>=ISREF(B11)</t>
+  </si>
+  <si>
+    <t>=ISREF(B12)</t>
+  </si>
+  <si>
+    <t>=ISREF(B13)</t>
+  </si>
+  <si>
+    <t>=ISREF(B14)</t>
+  </si>
+  <si>
+    <t>=ISREF(B15)</t>
+  </si>
+  <si>
+    <t>=ISREF(B16)</t>
+  </si>
+  <si>
+    <t>=ISREF(B17)</t>
+  </si>
+  <si>
+    <t>=ISREF(B18)</t>
+  </si>
+  <si>
+    <t>=ISREF(B19)</t>
+  </si>
+  <si>
+    <t>=ISREF(B20)</t>
+  </si>
+  <si>
+    <t>=ISREF(B21)</t>
+  </si>
+  <si>
+    <t>=ISREF(B22)</t>
+  </si>
+  <si>
+    <t>=ISREF(B23)</t>
+  </si>
+  <si>
+    <t>=ISREF(B24)</t>
+  </si>
+  <si>
+    <t>=ISREF(B25)</t>
+  </si>
+  <si>
+    <t>=ISREF(B26)</t>
+  </si>
+  <si>
+    <t>=ISREF(B27)</t>
+  </si>
+  <si>
+    <t>=ISREF(B28)</t>
+  </si>
+  <si>
+    <t>=ISREF(B29)</t>
+  </si>
+  <si>
+    <t>=ISREF(B30)</t>
+  </si>
+  <si>
+    <t>=ISREF(B31)</t>
+  </si>
+  <si>
+    <t>=ISREF(B32)</t>
+  </si>
+  <si>
+    <t>=ISREF(B33)</t>
   </si>
   <si>
     <t>INFORMATION AUDIT LAB: ISFORMULA (Formula Presence Audit)</t>
   </si>
   <si>
-    <t>Cell</t>
-  </si>
-  <si>
-    <t>Entry Type</t>
-  </si>
-  <si>
-    <t>Applied Formula</t>
-  </si>
-  <si>
-    <t>Audit Result</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>Formula Calculation</t>
-  </si>
-  <si>
-    <t>=ISFORMULA(C4)</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>Hardcoded Constant</t>
-  </si>
-  <si>
-    <t>=ISFORMULA(C5)</t>
+    <t>=ISFORMULA(B4)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B5)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B6)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B7)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B8)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B9)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B10)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B11)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B12)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B13)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B14)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B15)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B16)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B17)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B18)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B19)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B20)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B21)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B22)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B23)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B24)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B25)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B26)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B27)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B28)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B29)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B30)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B31)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B32)</t>
+  </si>
+  <si>
+    <t>=ISFORMULA(B33)</t>
   </si>
   <si>
     <t>INFORMATION AUDIT LAB: TYPE (Data Type Classification)</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Data Category</t>
-  </si>
-  <si>
-    <t>TYPE Code</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Barrackpore</t>
-  </si>
-  <si>
-    <t>Text</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Logical Boolean</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>=TYPE(B4)</t>
+  </si>
+  <si>
+    <t>=TYPE(B5)</t>
+  </si>
+  <si>
+    <t>=TYPE(B6)</t>
+  </si>
+  <si>
+    <t>=TYPE(B7)</t>
+  </si>
+  <si>
+    <t>=TYPE(B8)</t>
+  </si>
+  <si>
+    <t>=TYPE(B9)</t>
+  </si>
+  <si>
+    <t>=TYPE(B10)</t>
+  </si>
+  <si>
+    <t>=TYPE(B11)</t>
+  </si>
+  <si>
+    <t>=TYPE(B12)</t>
+  </si>
+  <si>
+    <t>=TYPE(B13)</t>
+  </si>
+  <si>
+    <t>=TYPE(B14)</t>
+  </si>
+  <si>
+    <t>=TYPE(B15)</t>
+  </si>
+  <si>
+    <t>=TYPE(B16)</t>
+  </si>
+  <si>
+    <t>=TYPE(B17)</t>
+  </si>
+  <si>
+    <t>=TYPE(B18)</t>
+  </si>
+  <si>
+    <t>=TYPE(B19)</t>
+  </si>
+  <si>
+    <t>=TYPE(B20)</t>
+  </si>
+  <si>
+    <t>=TYPE(B21)</t>
+  </si>
+  <si>
+    <t>=TYPE(B22)</t>
+  </si>
+  <si>
+    <t>=TYPE(B23)</t>
+  </si>
+  <si>
+    <t>=TYPE(B24)</t>
+  </si>
+  <si>
+    <t>=TYPE(B25)</t>
+  </si>
+  <si>
+    <t>=TYPE(B26)</t>
+  </si>
+  <si>
+    <t>=TYPE(B27)</t>
+  </si>
+  <si>
+    <t>=TYPE(B28)</t>
+  </si>
+  <si>
+    <t>=TYPE(B29)</t>
+  </si>
+  <si>
+    <t>=TYPE(B30)</t>
+  </si>
+  <si>
+    <t>=TYPE(B31)</t>
+  </si>
+  <si>
+    <t>=TYPE(B32)</t>
+  </si>
+  <si>
+    <t>=TYPE(B33)</t>
   </si>
   <si>
     <t>INFORMATION AUDIT LAB: FORMULATEXT (Formula Expression Audit)</t>
   </si>
   <si>
-    <t>Target Cell</t>
-  </si>
-  <si>
-    <t>Formula Content</t>
-  </si>
-  <si>
-    <t>Extracted Formula</t>
-  </si>
-  <si>
-    <t>E10</t>
-  </si>
-  <si>
-    <t>=SUM(B4:B9)</t>
-  </si>
-  <si>
-    <t>=FORMULATEXT(E10)</t>
+    <t>=FORMULATEXT(B4)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B5)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B6)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B7)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B8)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B9)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B10)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B11)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B12)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B13)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B14)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B15)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B16)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B17)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B18)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B19)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B20)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B21)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B22)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B23)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B24)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B25)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B26)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B27)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B28)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B29)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B30)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B31)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B32)</t>
+  </si>
+  <si>
+    <t>=FORMULATEXT(B33)</t>
   </si>
   <si>
     <t>INFORMATION AUDIT LAB: CELL (Cell Environment Metadata)</t>
   </si>
   <si>
-    <t>Info Type</t>
-  </si>
-  <si>
-    <t>Returned Value</t>
-  </si>
-  <si>
-    <t>filename</t>
-  </si>
-  <si>
-    <t>=CELL("filename", A1)</t>
-  </si>
-  <si>
-    <t>Active Workbook Path &amp; Sheet Name</t>
-  </si>
-  <si>
-    <t>address</t>
-  </si>
-  <si>
-    <t>=CELL("address", B4)</t>
-  </si>
-  <si>
-    <t>$B$4</t>
+    <t>=CELL(B4)</t>
+  </si>
+  <si>
+    <t>=CELL(B5)</t>
+  </si>
+  <si>
+    <t>=CELL(B6)</t>
+  </si>
+  <si>
+    <t>=CELL(B7)</t>
+  </si>
+  <si>
+    <t>=CELL(B8)</t>
+  </si>
+  <si>
+    <t>=CELL(B9)</t>
+  </si>
+  <si>
+    <t>=CELL(B10)</t>
+  </si>
+  <si>
+    <t>=CELL(B11)</t>
+  </si>
+  <si>
+    <t>=CELL(B12)</t>
+  </si>
+  <si>
+    <t>=CELL(B13)</t>
+  </si>
+  <si>
+    <t>=CELL(B14)</t>
+  </si>
+  <si>
+    <t>=CELL(B15)</t>
+  </si>
+  <si>
+    <t>=CELL(B16)</t>
+  </si>
+  <si>
+    <t>=CELL(B17)</t>
+  </si>
+  <si>
+    <t>=CELL(B18)</t>
+  </si>
+  <si>
+    <t>=CELL(B19)</t>
+  </si>
+  <si>
+    <t>=CELL(B20)</t>
+  </si>
+  <si>
+    <t>=CELL(B21)</t>
+  </si>
+  <si>
+    <t>=CELL(B22)</t>
+  </si>
+  <si>
+    <t>=CELL(B23)</t>
+  </si>
+  <si>
+    <t>=CELL(B24)</t>
+  </si>
+  <si>
+    <t>=CELL(B25)</t>
+  </si>
+  <si>
+    <t>=CELL(B26)</t>
+  </si>
+  <si>
+    <t>=CELL(B27)</t>
+  </si>
+  <si>
+    <t>=CELL(B28)</t>
+  </si>
+  <si>
+    <t>=CELL(B29)</t>
+  </si>
+  <si>
+    <t>=CELL(B30)</t>
+  </si>
+  <si>
+    <t>=CELL(B31)</t>
+  </si>
+  <si>
+    <t>=CELL(B32)</t>
+  </si>
+  <si>
+    <t>=CELL(B33)</t>
   </si>
   <si>
     <t>INFORMATION AUDIT LAB: INFO (System &amp; Calculation Environment)</t>
   </si>
   <si>
-    <t>Environment Type</t>
-  </si>
-  <si>
-    <t>Returned Output</t>
-  </si>
-  <si>
-    <t>recalc</t>
-  </si>
-  <si>
-    <t>=INFO("recalc")</t>
-  </si>
-  <si>
-    <t>Automatic</t>
-  </si>
-  <si>
-    <t>osversion</t>
-  </si>
-  <si>
-    <t>=INFO("osversion")</t>
-  </si>
-  <si>
-    <t>Windows (64-bit)</t>
+    <t>=INFO(B4)</t>
+  </si>
+  <si>
+    <t>=INFO(B5)</t>
+  </si>
+  <si>
+    <t>=INFO(B6)</t>
+  </si>
+  <si>
+    <t>=INFO(B7)</t>
+  </si>
+  <si>
+    <t>=INFO(B8)</t>
+  </si>
+  <si>
+    <t>=INFO(B9)</t>
+  </si>
+  <si>
+    <t>=INFO(B10)</t>
+  </si>
+  <si>
+    <t>=INFO(B11)</t>
+  </si>
+  <si>
+    <t>=INFO(B12)</t>
+  </si>
+  <si>
+    <t>=INFO(B13)</t>
+  </si>
+  <si>
+    <t>=INFO(B14)</t>
+  </si>
+  <si>
+    <t>=INFO(B15)</t>
+  </si>
+  <si>
+    <t>=INFO(B16)</t>
+  </si>
+  <si>
+    <t>=INFO(B17)</t>
+  </si>
+  <si>
+    <t>=INFO(B18)</t>
+  </si>
+  <si>
+    <t>=INFO(B19)</t>
+  </si>
+  <si>
+    <t>=INFO(B20)</t>
+  </si>
+  <si>
+    <t>=INFO(B21)</t>
+  </si>
+  <si>
+    <t>=INFO(B22)</t>
+  </si>
+  <si>
+    <t>=INFO(B23)</t>
+  </si>
+  <si>
+    <t>=INFO(B24)</t>
+  </si>
+  <si>
+    <t>=INFO(B25)</t>
+  </si>
+  <si>
+    <t>=INFO(B26)</t>
+  </si>
+  <si>
+    <t>=INFO(B27)</t>
+  </si>
+  <si>
+    <t>=INFO(B28)</t>
+  </si>
+  <si>
+    <t>=INFO(B29)</t>
+  </si>
+  <si>
+    <t>=INFO(B30)</t>
+  </si>
+  <si>
+    <t>=INFO(B31)</t>
+  </si>
+  <si>
+    <t>=INFO(B32)</t>
+  </si>
+  <si>
+    <t>=INFO(B33)</t>
   </si>
 </sst>
 </file>
@@ -413,7 +1148,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FDC2626"/>
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -432,7 +1167,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -440,41 +1175,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF334155"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF334155"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF0F172A"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF0F172A"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFE2E8F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFE2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFE2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFE2E8F0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -484,40 +1189,34 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1029,10 +1728,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="22" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1084,14 +1785,406 @@
       <c r="A5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="8">
-        <v>145000</v>
+      <c r="B5" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1109,10 +2202,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="22" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1125,7 +2220,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1133,16 +2228,16 @@
       <c r="E2" s="4"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1150,11 +2245,11 @@
       <c r="A4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="10">
-        <v>98000</v>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>39</v>
@@ -1165,13 +2260,405 @@
         <v>40</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>42</v>
+      <c r="C6" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1189,12 +2676,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="3" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1207,44 +2694,445 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+    <row r="3" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="C7" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>42</v>
+      <c r="C8" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1262,11 +3150,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1280,7 +3168,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1288,28 +3176,28 @@
       <c r="E2" s="4"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>57</v>
+      <c r="A3" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>60</v>
+        <v>191</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>39</v>
@@ -1317,16 +3205,408 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>42</v>
+      <c r="C12" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1344,10 +3624,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="22" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1360,55 +3642,445 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>64</v>
+        <v>221</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+    <row r="3" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="10">
-        <v>145.89</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="C13" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="B14" s="6" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="C14" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="B15" s="7" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="C15" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>74</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1426,11 +4098,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1443,33 +4117,445 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>75</v>
+        <v>252</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B3" s="14" t="s">
+    <row r="3" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="B17" s="7" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="C17" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="B18" s="6" t="s">
         <v>81</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1487,12 +4573,12 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="39" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1505,44 +4591,445 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+    <row r="3" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="15" t="s">
+      <c r="B19" s="7" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="C19" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="B20" s="6" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="C20" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="B21" s="7" t="s">
         <v>90</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1560,12 +5047,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1578,44 +5065,445 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>91</v>
+        <v>314</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+    <row r="3" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="16" t="s">
+      <c r="B22" s="6" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="C22" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="C23" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>99</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
